--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -2327,115 +2327,307 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
+      <c r="A96" s="2" t="n">
+        <v>46208</v>
+      </c>
       <c r="B96" s="3">
         <f>IF(A96="","",TEXT(A96,"ddd"))</f>
         <v/>
       </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pasta arrabbiata</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
+      <c r="A97" s="2" t="n">
+        <v>46209</v>
+      </c>
       <c r="B97" s="3">
         <f>IF(A97="","",TEXT(A97,"ddd"))</f>
         <v/>
       </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Pulled pork burger</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
+      <c r="A98" s="2" t="n">
+        <v>46209</v>
+      </c>
       <c r="B98" s="3">
         <f>IF(A98="","",TEXT(A98,"ddd"))</f>
         <v/>
       </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Spanish omelette</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n"/>
+      <c r="A99" s="2" t="n">
+        <v>46210</v>
+      </c>
       <c r="B99" s="3">
         <f>IF(A99="","",TEXT(A99,"ddd"))</f>
         <v/>
       </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Watercress pork rib soup</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n"/>
+      <c r="A100" s="2" t="n">
+        <v>46210</v>
+      </c>
       <c r="B100" s="3">
         <f>IF(A100="","",TEXT(A100,"ddd"))</f>
         <v/>
       </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Braised pork with tofu and egg (Tau Yu Bak)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n"/>
+      <c r="A101" s="2" t="n">
+        <v>46210</v>
+      </c>
       <c r="B101" s="3">
         <f>IF(A101="","",TEXT(A101,"ddd"))</f>
         <v/>
       </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Steamed pomfret</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n"/>
+      <c r="A102" s="2" t="n">
+        <v>46211</v>
+      </c>
       <c r="B102" s="3">
         <f>IF(A102="","",TEXT(A102,"ddd"))</f>
         <v/>
       </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Frozen prata</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n"/>
+      <c r="A103" s="2" t="n">
+        <v>46211</v>
+      </c>
       <c r="B103" s="3">
         <f>IF(A103="","",TEXT(A103,"ddd"))</f>
         <v/>
       </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Padang chicken curry</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n"/>
+      <c r="A104" s="2" t="n">
+        <v>46212</v>
+      </c>
       <c r="B104" s="3">
         <f>IF(A104="","",TEXT(A104,"ddd"))</f>
         <v/>
       </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Nasi lemak</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n"/>
+      <c r="A105" s="2" t="n">
+        <v>46212</v>
+      </c>
       <c r="B105" s="3">
         <f>IF(A105="","",TEXT(A105,"ddd"))</f>
         <v/>
       </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fried chicken wings</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n"/>
+      <c r="A106" s="2" t="n">
+        <v>46212</v>
+      </c>
       <c r="B106" s="3">
         <f>IF(A106="","",TEXT(A106,"ddd"))</f>
         <v/>
       </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Egg omelette</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n"/>
+      <c r="A107" s="2" t="n">
+        <v>46212</v>
+      </c>
       <c r="B107" s="3">
         <f>IF(A107="","",TEXT(A107,"ddd"))</f>
         <v/>
       </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sambal long beans</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026) — sambal kangkong recipe w/ long beans</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n"/>
+      <c r="A108" s="2" t="n">
+        <v>46212</v>
+      </c>
       <c r="B108" s="3">
         <f>IF(A108="","",TEXT(A108,"ddd"))</f>
         <v/>
       </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Begedil</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n"/>
+      <c r="A109" s="2" t="n">
+        <v>46213</v>
+      </c>
       <c r="B109" s="3">
         <f>IF(A109="","",TEXT(A109,"ddd"))</f>
         <v/>
       </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Grilled cheese</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n"/>
+      <c r="A110" s="2" t="n">
+        <v>46213</v>
+      </c>
       <c r="B110" s="3">
         <f>IF(A110="","",TEXT(A110,"ddd"))</f>
         <v/>
       </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Tomato soup</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n"/>
+      <c r="A111" s="2" t="n">
+        <v>46213</v>
+      </c>
       <c r="B111" s="3">
         <f>IF(A111="","",TEXT(A111,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fries</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>planned (week of 6 Jul 2026)</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3778,7 +3970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7687,6 +7879,378 @@
       </c>
       <c r="G128">
         <f>IF(C128="","Never cooked",IF(D128&lt;F128,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Pasta arrabbiata</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="C129">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A129)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A129)),"")</f>
+        <v/>
+      </c>
+      <c r="D129">
+        <f>IF(C129="","",TODAY()-C129)</f>
+        <v/>
+      </c>
+      <c r="E129">
+        <f>COUNTIF('Cook log'!C2:C1000,A129)</f>
+        <v/>
+      </c>
+      <c r="F129" t="n">
+        <v>21</v>
+      </c>
+      <c r="G129">
+        <f>IF(C129="","Never cooked",IF(D129&lt;F129,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Pulled pork burger</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C130">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A130)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A130)),"")</f>
+        <v/>
+      </c>
+      <c r="D130">
+        <f>IF(C130="","",TODAY()-C130)</f>
+        <v/>
+      </c>
+      <c r="E130">
+        <f>COUNTIF('Cook log'!C2:C1000,A130)</f>
+        <v/>
+      </c>
+      <c r="F130" t="n">
+        <v>21</v>
+      </c>
+      <c r="G130">
+        <f>IF(C130="","Never cooked",IF(D130&lt;F130,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Spanish omelette</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Egg</t>
+        </is>
+      </c>
+      <c r="C131">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A131)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A131)),"")</f>
+        <v/>
+      </c>
+      <c r="D131">
+        <f>IF(C131="","",TODAY()-C131)</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>COUNTIF('Cook log'!C2:C1000,A131)</f>
+        <v/>
+      </c>
+      <c r="F131" t="n">
+        <v>21</v>
+      </c>
+      <c r="G131">
+        <f>IF(C131="","Never cooked",IF(D131&lt;F131,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Luncheon meat &amp; potatoes</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C132">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A132)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A132)),"")</f>
+        <v/>
+      </c>
+      <c r="D132">
+        <f>IF(C132="","",TODAY()-C132)</f>
+        <v/>
+      </c>
+      <c r="E132">
+        <f>COUNTIF('Cook log'!C2:C1000,A132)</f>
+        <v/>
+      </c>
+      <c r="F132" t="n">
+        <v>21</v>
+      </c>
+      <c r="G132">
+        <f>IF(C132="","Never cooked",IF(D132&lt;F132,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Frozen prata</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C133">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A133)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A133)),"")</f>
+        <v/>
+      </c>
+      <c r="D133">
+        <f>IF(C133="","",TODAY()-C133)</f>
+        <v/>
+      </c>
+      <c r="E133">
+        <f>COUNTIF('Cook log'!C2:C1000,A133)</f>
+        <v/>
+      </c>
+      <c r="F133" t="n">
+        <v>21</v>
+      </c>
+      <c r="G133">
+        <f>IF(C133="","Never cooked",IF(D133&lt;F133,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Padang chicken curry</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="C134">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A134)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A134)),"")</f>
+        <v/>
+      </c>
+      <c r="D134">
+        <f>IF(C134="","",TODAY()-C134)</f>
+        <v/>
+      </c>
+      <c r="E134">
+        <f>COUNTIF('Cook log'!C2:C1000,A134)</f>
+        <v/>
+      </c>
+      <c r="F134" t="n">
+        <v>21</v>
+      </c>
+      <c r="G134">
+        <f>IF(C134="","Never cooked",IF(D134&lt;F134,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sambal long beans</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C135">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A135)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A135)),"")</f>
+        <v/>
+      </c>
+      <c r="D135">
+        <f>IF(C135="","",TODAY()-C135)</f>
+        <v/>
+      </c>
+      <c r="E135">
+        <f>COUNTIF('Cook log'!C2:C1000,A135)</f>
+        <v/>
+      </c>
+      <c r="F135" t="n">
+        <v>21</v>
+      </c>
+      <c r="G135">
+        <f>IF(C135="","Never cooked",IF(D135&lt;F135,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Begedil</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C136">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A136)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A136)),"")</f>
+        <v/>
+      </c>
+      <c r="D136">
+        <f>IF(C136="","",TODAY()-C136)</f>
+        <v/>
+      </c>
+      <c r="E136">
+        <f>COUNTIF('Cook log'!C2:C1000,A136)</f>
+        <v/>
+      </c>
+      <c r="F136" t="n">
+        <v>21</v>
+      </c>
+      <c r="G136">
+        <f>IF(C136="","Never cooked",IF(D136&lt;F136,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Grilled cheese</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="C137">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A137)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A137)),"")</f>
+        <v/>
+      </c>
+      <c r="D137">
+        <f>IF(C137="","",TODAY()-C137)</f>
+        <v/>
+      </c>
+      <c r="E137">
+        <f>COUNTIF('Cook log'!C2:C1000,A137)</f>
+        <v/>
+      </c>
+      <c r="F137" t="n">
+        <v>21</v>
+      </c>
+      <c r="G137">
+        <f>IF(C137="","Never cooked",IF(D137&lt;F137,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Tomato soup</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Soup</t>
+        </is>
+      </c>
+      <c r="C138">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A138)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A138)),"")</f>
+        <v/>
+      </c>
+      <c r="D138">
+        <f>IF(C138="","",TODAY()-C138)</f>
+        <v/>
+      </c>
+      <c r="E138">
+        <f>COUNTIF('Cook log'!C2:C1000,A138)</f>
+        <v/>
+      </c>
+      <c r="F138" t="n">
+        <v>21</v>
+      </c>
+      <c r="G138">
+        <f>IF(C138="","Never cooked",IF(D138&lt;F138,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Fries</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C139">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A139)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A139)),"")</f>
+        <v/>
+      </c>
+      <c r="D139">
+        <f>IF(C139="","",TODAY()-C139)</f>
+        <v/>
+      </c>
+      <c r="E139">
+        <f>COUNTIF('Cook log'!C2:C1000,A139)</f>
+        <v/>
+      </c>
+      <c r="F139" t="n">
+        <v>21</v>
+      </c>
+      <c r="G139">
+        <f>IF(C139="","Never cooked",IF(D139&lt;F139,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Braised pork with tofu and egg (Tau Yu Bak)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C140">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A140)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A140)),"")</f>
+        <v/>
+      </c>
+      <c r="D140">
+        <f>IF(C140="","",TODAY()-C140)</f>
+        <v/>
+      </c>
+      <c r="E140">
+        <f>COUNTIF('Cook log'!C2:C1000,A140)</f>
+        <v/>
+      </c>
+      <c r="F140" t="n">
+        <v>21</v>
+      </c>
+      <c r="G140">
+        <f>IF(C140="","Never cooked",IF(D140&lt;F140,"Cooldown","Due"))</f>
         <v/>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -2631,171 +2631,459 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n"/>
+      <c r="A112" s="2" t="n">
+        <v>46216</v>
+      </c>
       <c r="B112" s="3">
         <f>IF(A112="","",TEXT(A112,"ddd"))</f>
         <v/>
       </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Dry laksa</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n"/>
+      <c r="A113" s="2" t="n">
+        <v>46216</v>
+      </c>
       <c r="B113" s="3">
         <f>IF(A113="","",TEXT(A113,"ddd"))</f>
         <v/>
       </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Fishball minced pork soup</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n"/>
+      <c r="A114" s="2" t="n">
+        <v>46217</v>
+      </c>
       <c r="B114" s="3">
         <f>IF(A114="","",TEXT(A114,"ddd"))</f>
         <v/>
       </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Japanese hamburg patty</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n"/>
+      <c r="A115" s="2" t="n">
+        <v>46217</v>
+      </c>
       <c r="B115" s="3">
         <f>IF(A115="","",TEXT(A115,"ddd"))</f>
         <v/>
       </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n"/>
+      <c r="A116" s="2" t="n">
+        <v>46217</v>
+      </c>
       <c r="B116" s="3">
         <f>IF(A116="","",TEXT(A116,"ddd"))</f>
         <v/>
       </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Stir fried dou miao</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n"/>
+      <c r="A117" s="2" t="n">
+        <v>46218</v>
+      </c>
       <c r="B117" s="3">
         <f>IF(A117="","",TEXT(A117,"ddd"))</f>
         <v/>
       </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Macau Portuguese chicken rice</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n"/>
+      <c r="A118" s="2" t="n">
+        <v>46218</v>
+      </c>
       <c r="B118" s="3">
         <f>IF(A118="","",TEXT(A118,"ddd"))</f>
         <v/>
       </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ABC soup</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n"/>
+      <c r="A119" s="2" t="n">
+        <v>46219</v>
+      </c>
       <c r="B119" s="3">
         <f>IF(A119="","",TEXT(A119,"ddd"))</f>
         <v/>
       </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026) — with curry</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n"/>
+      <c r="A120" s="2" t="n">
+        <v>46219</v>
+      </c>
       <c r="B120" s="3">
         <f>IF(A120="","",TEXT(A120,"ddd"))</f>
         <v/>
       </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Chicken curry</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n"/>
+      <c r="A121" s="2" t="n">
+        <v>46220</v>
+      </c>
       <c r="B121" s="3">
         <f>IF(A121="","",TEXT(A121,"ddd"))</f>
         <v/>
       </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Baby back ribs</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n"/>
+      <c r="A122" s="2" t="n">
+        <v>46220</v>
+      </c>
       <c r="B122" s="3">
         <f>IF(A122="","",TEXT(A122,"ddd"))</f>
         <v/>
       </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cornbread</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n"/>
+      <c r="A123" s="2" t="n">
+        <v>46220</v>
+      </c>
       <c r="B123" s="3">
         <f>IF(A123="","",TEXT(A123,"ddd"))</f>
         <v/>
       </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Creamed spinach</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>planned (week of 13 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n"/>
+      <c r="A124" s="2" t="n">
+        <v>46223</v>
+      </c>
       <c r="B124" s="3">
         <f>IF(A124="","",TEXT(A124,"ddd"))</f>
         <v/>
       </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sticky pork belly</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n"/>
+      <c r="A125" s="2" t="n">
+        <v>46223</v>
+      </c>
       <c r="B125" s="3">
         <f>IF(A125="","",TEXT(A125,"ddd"))</f>
         <v/>
       </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n"/>
+      <c r="A126" s="2" t="n">
+        <v>46223</v>
+      </c>
       <c r="B126" s="3">
         <f>IF(A126="","",TEXT(A126,"ddd"))</f>
         <v/>
       </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Winter melon pork rib soup</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n"/>
+      <c r="A127" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="B127" s="3">
         <f>IF(A127="","",TEXT(A127,"ddd"))</f>
         <v/>
       </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Teriyaki chicken cutlet</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n"/>
+      <c r="A128" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="B128" s="3">
         <f>IF(A128="","",TEXT(A128,"ddd"))</f>
         <v/>
       </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Rösti</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n"/>
+      <c r="A129" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="B129" s="3">
         <f>IF(A129="","",TEXT(A129,"ddd"))</f>
         <v/>
       </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Broccoli stir fry with mushroom</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n"/>
+      <c r="A130" s="2" t="n">
+        <v>46225</v>
+      </c>
       <c r="B130" s="3">
         <f>IF(A130="","",TEXT(A130,"ddd"))</f>
         <v/>
       </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Hokkien hai fan (ah gong)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n"/>
+      <c r="A131" s="2" t="n">
+        <v>46226</v>
+      </c>
       <c r="B131" s="3">
         <f>IF(A131="","",TEXT(A131,"ddd"))</f>
         <v/>
       </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Pork rib king</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n"/>
+      <c r="A132" s="2" t="n">
+        <v>46226</v>
+      </c>
       <c r="B132" s="3">
         <f>IF(A132="","",TEXT(A132,"ddd"))</f>
         <v/>
       </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Steamed egg (ah gong style)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n"/>
+      <c r="A133" s="2" t="n">
+        <v>46226</v>
+      </c>
       <c r="B133" s="3">
         <f>IF(A133="","",TEXT(A133,"ddd"))</f>
         <v/>
       </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Stir-fried baby bok choy</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n"/>
+      <c r="A134" s="2" t="n">
+        <v>46227</v>
+      </c>
       <c r="B134" s="3">
         <f>IF(A134="","",TEXT(A134,"ddd"))</f>
         <v/>
       </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Stir fried bee hoon</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026) — no prawns</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n"/>
+      <c r="A135" s="2" t="n">
+        <v>46227</v>
+      </c>
       <c r="B135" s="3">
         <f>IF(A135="","",TEXT(A135,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Fried chicken wings</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>planned (week of 20 Jul 2026)</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -3970,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8251,6 +8539,347 @@
       </c>
       <c r="G140">
         <f>IF(C140="","Never cooked",IF(D140&lt;F140,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Dry laksa</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Noodle</t>
+        </is>
+      </c>
+      <c r="C141">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A141)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A141)),"")</f>
+        <v/>
+      </c>
+      <c r="D141">
+        <f>IF(C141="","",TODAY()-C141)</f>
+        <v/>
+      </c>
+      <c r="E141">
+        <f>COUNTIF('Cook log'!C2:C1000,A141)</f>
+        <v/>
+      </c>
+      <c r="F141" t="n">
+        <v>21</v>
+      </c>
+      <c r="G141">
+        <f>IF(C141="","Never cooked",IF(D141&lt;F141,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Japanese hamburg patty</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="C142">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A142)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A142)),"")</f>
+        <v/>
+      </c>
+      <c r="D142">
+        <f>IF(C142="","",TODAY()-C142)</f>
+        <v/>
+      </c>
+      <c r="E142">
+        <f>COUNTIF('Cook log'!C2:C1000,A142)</f>
+        <v/>
+      </c>
+      <c r="F142" t="n">
+        <v>21</v>
+      </c>
+      <c r="G142">
+        <f>IF(C142="","Never cooked",IF(D142&lt;F142,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Dry mee siam</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Noodle</t>
+        </is>
+      </c>
+      <c r="C143">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A143)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A143)),"")</f>
+        <v/>
+      </c>
+      <c r="D143">
+        <f>IF(C143="","",TODAY()-C143)</f>
+        <v/>
+      </c>
+      <c r="E143">
+        <f>COUNTIF('Cook log'!C2:C1000,A143)</f>
+        <v/>
+      </c>
+      <c r="F143" t="n">
+        <v>21</v>
+      </c>
+      <c r="G143">
+        <f>IF(C143="","Never cooked",IF(D143&lt;F143,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Chicken curry</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="C144">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A144)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A144)),"")</f>
+        <v/>
+      </c>
+      <c r="D144">
+        <f>IF(C144="","",TODAY()-C144)</f>
+        <v/>
+      </c>
+      <c r="E144">
+        <f>COUNTIF('Cook log'!C2:C1000,A144)</f>
+        <v/>
+      </c>
+      <c r="F144" t="n">
+        <v>21</v>
+      </c>
+      <c r="G144">
+        <f>IF(C144="","Never cooked",IF(D144&lt;F144,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Baby back ribs</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C145">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A145)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A145)),"")</f>
+        <v/>
+      </c>
+      <c r="D145">
+        <f>IF(C145="","",TODAY()-C145)</f>
+        <v/>
+      </c>
+      <c r="E145">
+        <f>COUNTIF('Cook log'!C2:C1000,A145)</f>
+        <v/>
+      </c>
+      <c r="F145" t="n">
+        <v>21</v>
+      </c>
+      <c r="G145">
+        <f>IF(C145="","Never cooked",IF(D145&lt;F145,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Cornbread</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C146">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A146)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A146)),"")</f>
+        <v/>
+      </c>
+      <c r="D146">
+        <f>IF(C146="","",TODAY()-C146)</f>
+        <v/>
+      </c>
+      <c r="E146">
+        <f>COUNTIF('Cook log'!C2:C1000,A146)</f>
+        <v/>
+      </c>
+      <c r="F146" t="n">
+        <v>21</v>
+      </c>
+      <c r="G146">
+        <f>IF(C146="","Never cooked",IF(D146&lt;F146,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Creamed spinach</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C147">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A147)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A147)),"")</f>
+        <v/>
+      </c>
+      <c r="D147">
+        <f>IF(C147="","",TODAY()-C147)</f>
+        <v/>
+      </c>
+      <c r="E147">
+        <f>COUNTIF('Cook log'!C2:C1000,A147)</f>
+        <v/>
+      </c>
+      <c r="F147" t="n">
+        <v>21</v>
+      </c>
+      <c r="G147">
+        <f>IF(C147="","Never cooked",IF(D147&lt;F147,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C148">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A148)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A148)),"")</f>
+        <v/>
+      </c>
+      <c r="D148">
+        <f>IF(C148="","",TODAY()-C148)</f>
+        <v/>
+      </c>
+      <c r="E148">
+        <f>COUNTIF('Cook log'!C2:C1000,A148)</f>
+        <v/>
+      </c>
+      <c r="F148" t="n">
+        <v>14</v>
+      </c>
+      <c r="G148">
+        <f>IF(C148="","Never cooked",IF(D148&lt;F148,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C149">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A149)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A149)),"")</f>
+        <v/>
+      </c>
+      <c r="D149">
+        <f>IF(C149="","",TODAY()-C149)</f>
+        <v/>
+      </c>
+      <c r="E149">
+        <f>COUNTIF('Cook log'!C2:C1000,A149)</f>
+        <v/>
+      </c>
+      <c r="F149" t="n">
+        <v>14</v>
+      </c>
+      <c r="G149">
+        <f>IF(C149="","Never cooked",IF(D149&lt;F149,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Hokkien hai fan (ah gong)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C150">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A150)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A150)),"")</f>
+        <v/>
+      </c>
+      <c r="D150">
+        <f>IF(C150="","",TODAY()-C150)</f>
+        <v/>
+      </c>
+      <c r="E150">
+        <f>COUNTIF('Cook log'!C2:C1000,A150)</f>
+        <v/>
+      </c>
+      <c r="F150" t="n">
+        <v>21</v>
+      </c>
+      <c r="G150">
+        <f>IF(C150="","Never cooked",IF(D150&lt;F150,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Stir-fried baby bok choy</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C151">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A151)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A151)),"")</f>
+        <v/>
+      </c>
+      <c r="D151">
+        <f>IF(C151="","",TODAY()-C151)</f>
+        <v/>
+      </c>
+      <c r="E151">
+        <f>COUNTIF('Cook log'!C2:C1000,A151)</f>
+        <v/>
+      </c>
+      <c r="F151" t="n">
+        <v>14</v>
+      </c>
+      <c r="G151">
+        <f>IF(C151="","Never cooked",IF(D151&lt;F151,"Cooldown","Due"))</f>
         <v/>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Teriyaki chicken cutlet</t>
+          <t>Cheese sausage</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Hokkien hai fan (ah gong)</t>
+          <t>Egg fried rice with char siew</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Steamed egg (ah gong style)</t>
+          <t>ABC soup</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>planned (week of 20 Jul 2026)</t>
+          <t>planned (week of 20 Jul 2026) — no tomato</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H151"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8880,6 +8880,68 @@
       </c>
       <c r="G151">
         <f>IF(C151="","Never cooked",IF(D151&lt;F151,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Cheese sausage</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C152">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A152)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A152)),"")</f>
+        <v/>
+      </c>
+      <c r="D152">
+        <f>IF(C152="","",TODAY()-C152)</f>
+        <v/>
+      </c>
+      <c r="E152">
+        <f>COUNTIF('Cook log'!C2:C1000,A152)</f>
+        <v/>
+      </c>
+      <c r="F152" t="n">
+        <v>14</v>
+      </c>
+      <c r="G152">
+        <f>IF(C152="","Never cooked",IF(D152&lt;F152,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Egg fried rice with char siew</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C153">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A153)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A153)),"")</f>
+        <v/>
+      </c>
+      <c r="D153">
+        <f>IF(C153="","",TODAY()-C153)</f>
+        <v/>
+      </c>
+      <c r="E153">
+        <f>COUNTIF('Cook log'!C2:C1000,A153)</f>
+        <v/>
+      </c>
+      <c r="F153" t="n">
+        <v>21</v>
+      </c>
+      <c r="G153">
+        <f>IF(C153="","Never cooked",IF(D153&lt;F153,"Cooldown","Due"))</f>
         <v/>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -3087,178 +3087,478 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n"/>
+      <c r="A136" s="2" t="n">
+        <v>46230</v>
+      </c>
       <c r="B136" s="3">
         <f>IF(A136="","",TEXT(A136,"ddd"))</f>
         <v/>
       </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Udon</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n"/>
+      <c r="A137" s="2" t="n">
+        <v>46230</v>
+      </c>
       <c r="B137" s="3">
         <f>IF(A137="","",TEXT(A137,"ddd"))</f>
         <v/>
       </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Yasai tempura</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n"/>
+      <c r="A138" s="2" t="n">
+        <v>46231</v>
+      </c>
       <c r="B138" s="3">
         <f>IF(A138="","",TEXT(A138,"ddd"))</f>
         <v/>
       </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Chicken tsukune</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n"/>
+      <c r="A139" s="2" t="n">
+        <v>46231</v>
+      </c>
       <c r="B139" s="3">
         <f>IF(A139="","",TEXT(A139,"ddd"))</f>
         <v/>
       </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n"/>
+      <c r="A140" s="2" t="n">
+        <v>46231</v>
+      </c>
       <c r="B140" s="3">
         <f>IF(A140="","",TEXT(A140,"ddd"))</f>
         <v/>
       </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Chinese yam and chicken soup</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026) — pork-rib version</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n"/>
+      <c r="A141" s="2" t="n">
+        <v>46232</v>
+      </c>
       <c r="B141" s="3">
         <f>IF(A141="","",TEXT(A141,"ddd"))</f>
         <v/>
       </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pork congee with dried scallop</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n"/>
+      <c r="A142" s="2" t="n">
+        <v>46232</v>
+      </c>
       <c r="B142" s="3">
         <f>IF(A142="","",TEXT(A142,"ddd"))</f>
         <v/>
       </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Youtiao</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n"/>
+      <c r="A143" s="2" t="n">
+        <v>46232</v>
+      </c>
       <c r="B143" s="3">
         <f>IF(A143="","",TEXT(A143,"ddd"))</f>
         <v/>
       </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026) — cooked green</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n"/>
+      <c r="A144" s="2" t="n">
+        <v>46233</v>
+      </c>
       <c r="B144" s="3">
         <f>IF(A144="","",TEXT(A144,"ddd"))</f>
         <v/>
       </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Kong bak pau (braised pork buns)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n"/>
+      <c r="A145" s="2" t="n">
+        <v>46233</v>
+      </c>
       <c r="B145" s="3">
         <f>IF(A145="","",TEXT(A145,"ddd"))</f>
         <v/>
       </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Hot and sour soup</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n"/>
+      <c r="A146" s="2" t="n">
+        <v>46234</v>
+      </c>
       <c r="B146" s="3">
         <f>IF(A146="","",TEXT(A146,"ddd"))</f>
         <v/>
       </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Yang Zhou fried rice</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026) — no prawns</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n"/>
+      <c r="A147" s="2" t="n">
+        <v>46234</v>
+      </c>
       <c r="B147" s="3">
         <f>IF(A147="","",TEXT(A147,"ddd"))</f>
         <v/>
       </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Old cucumber pork rib soup</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>planned (week of 27 Jul 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n"/>
+      <c r="A148" s="2" t="n">
+        <v>46237</v>
+      </c>
       <c r="B148" s="3">
         <f>IF(A148="","",TEXT(A148,"ddd"))</f>
         <v/>
       </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Taiwanese braised pork rice</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n"/>
+      <c r="A149" s="2" t="n">
+        <v>46238</v>
+      </c>
       <c r="B149" s="3">
         <f>IF(A149="","",TEXT(A149,"ddd"))</f>
         <v/>
       </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Thai style steamed seabass</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - Thai style steamed fish</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n"/>
+      <c r="A150" s="2" t="n">
+        <v>46238</v>
+      </c>
       <c r="B150" s="3">
         <f>IF(A150="","",TEXT(A150,"ddd"))</f>
         <v/>
       </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Eggplant with minced pork</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - yu xiang qie zi</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n"/>
+      <c r="A151" s="2" t="n">
+        <v>46238</v>
+      </c>
       <c r="B151" s="3">
         <f>IF(A151="","",TEXT(A151,"ddd"))</f>
         <v/>
       </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lotus root pork rib soup</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n"/>
+      <c r="A152" s="2" t="n">
+        <v>46239</v>
+      </c>
       <c r="B152" s="3">
         <f>IF(A152="","",TEXT(A152,"ddd"))</f>
         <v/>
       </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ee-fu mee</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n"/>
+      <c r="A153" s="2" t="n">
+        <v>46239</v>
+      </c>
       <c r="B153" s="3">
         <f>IF(A153="","",TEXT(A153,"ddd"))</f>
         <v/>
       </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Claypot tofu (tofu hotplate with broccoli)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - broccoli not snow peas; omit prawns; sub the Shaoxing</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n"/>
+      <c r="A154" s="2" t="n">
+        <v>46239</v>
+      </c>
       <c r="B154" s="3">
         <f>IF(A154="","",TEXT(A154,"ddd"))</f>
         <v/>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Chinese yam and chicken soup</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - sub the cooking wine</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n"/>
+      <c r="A155" s="2" t="n">
+        <v>46240</v>
+      </c>
       <c r="B155" s="3">
         <f>IF(A155="","",TEXT(A155,"ddd"))</f>
         <v/>
       </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Beef rendang</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - Madam Kwan's paste, 1.5 packets</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n"/>
+      <c r="A156" s="2" t="n">
+        <v>46240</v>
+      </c>
       <c r="B156" s="3">
         <f>IF(A156="","",TEXT(A156,"ddd"))</f>
         <v/>
       </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Steamed stuffed tofu puffs</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n"/>
+      <c r="A157" s="2" t="n">
+        <v>46240</v>
+      </c>
       <c r="B157" s="3">
         <f>IF(A157="","",TEXT(A157,"ddd"))</f>
         <v/>
       </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026) - dark leafy green, unseasoned</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n"/>
+      <c r="A158" s="2" t="n">
+        <v>46241</v>
+      </c>
       <c r="B158" s="3">
         <f>IF(A158="","",TEXT(A158,"ddd"))</f>
         <v/>
       </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Hakka mei cai kou rou</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n"/>
+      <c r="A159" s="2" t="n">
+        <v>46241</v>
+      </c>
       <c r="B159" s="3">
         <f>IF(A159="","",TEXT(A159,"ddd"))</f>
         <v/>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n"/>
+      <c r="A160" s="2" t="n">
+        <v>46241</v>
+      </c>
       <c r="B160" s="3">
         <f>IF(A160="","",TEXT(A160,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>planned (week of 3 Aug 2026)</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -4258,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6010,36 +6310,14 @@
       <c r="H54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Tofu hotplate with broccoli</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Vegetable</t>
-        </is>
-      </c>
-      <c r="C55" s="5">
-        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A55)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A55)),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="4">
-        <f>IF(C55="","",TODAY()-C55)</f>
-        <v/>
-      </c>
-      <c r="E55" s="4">
-        <f>COUNTIF('Cook log'!C2:C1000,A55)</f>
-        <v/>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="G55" s="6">
-        <f>IF(C55="","Never cooked",IF(D55&lt;F55,"Cooldown","Due"))</f>
-        <v/>
-      </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="6" t="n"/>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6954,7 +7232,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Claypot tofu</t>
+          <t>Claypot tofu (tofu hotplate with broccoli)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6983,7 +7261,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Egg tofu, doubanjiang, minced pork, prawns</t>
+          <t>recipes/claypot-tofu.md. Broccoli substitutes the snow peas. Merged with the old "Tofu hotplate with broccoli" row - same dish</t>
         </is>
       </c>
     </row>
@@ -8943,6 +9221,558 @@
       <c r="G153">
         <f>IF(C153="","Never cooked",IF(D153&lt;F153,"Cooldown","Due"))</f>
         <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Udon</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Noodle</t>
+        </is>
+      </c>
+      <c r="C154">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A154)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A154)),"")</f>
+        <v/>
+      </c>
+      <c r="D154">
+        <f>IF(C154="","",TODAY()-C154)</f>
+        <v/>
+      </c>
+      <c r="E154">
+        <f>COUNTIF('Cook log'!C2:C1000,A154)</f>
+        <v/>
+      </c>
+      <c r="F154" t="n">
+        <v>21</v>
+      </c>
+      <c r="G154">
+        <f>IF(C154="","Never cooked",IF(D154&lt;F154,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Yasai tempura</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C155">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A155)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A155)),"")</f>
+        <v/>
+      </c>
+      <c r="D155">
+        <f>IF(C155="","",TODAY()-C155)</f>
+        <v/>
+      </c>
+      <c r="E155">
+        <f>COUNTIF('Cook log'!C2:C1000,A155)</f>
+        <v/>
+      </c>
+      <c r="F155" t="n">
+        <v>21</v>
+      </c>
+      <c r="G155">
+        <f>IF(C155="","Never cooked",IF(D155&lt;F155,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>HK-style steamed chicken</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="C156">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A156)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A156)),"")</f>
+        <v/>
+      </c>
+      <c r="D156">
+        <f>IF(C156="","",TODAY()-C156)</f>
+        <v/>
+      </c>
+      <c r="E156">
+        <f>COUNTIF('Cook log'!C2:C1000,A156)</f>
+        <v/>
+      </c>
+      <c r="F156" t="n">
+        <v>21</v>
+      </c>
+      <c r="G156">
+        <f>IF(C156="","Never cooked",IF(D156&lt;F156,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Pork congee with dried scallop</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C157">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A157)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A157)),"")</f>
+        <v/>
+      </c>
+      <c r="D157">
+        <f>IF(C157="","",TODAY()-C157)</f>
+        <v/>
+      </c>
+      <c r="E157">
+        <f>COUNTIF('Cook log'!C2:C1000,A157)</f>
+        <v/>
+      </c>
+      <c r="F157" t="n">
+        <v>21</v>
+      </c>
+      <c r="G157">
+        <f>IF(C157="","Never cooked",IF(D157&lt;F157,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Youtiao</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="C158">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A158)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A158)),"")</f>
+        <v/>
+      </c>
+      <c r="D158">
+        <f>IF(C158="","",TODAY()-C158)</f>
+        <v/>
+      </c>
+      <c r="E158">
+        <f>COUNTIF('Cook log'!C2:C1000,A158)</f>
+        <v/>
+      </c>
+      <c r="F158" t="n">
+        <v>14</v>
+      </c>
+      <c r="G158">
+        <f>IF(C158="","Never cooked",IF(D158&lt;F158,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Kong bak pau (braised pork buns)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C159">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A159)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A159)),"")</f>
+        <v/>
+      </c>
+      <c r="D159">
+        <f>IF(C159="","",TODAY()-C159)</f>
+        <v/>
+      </c>
+      <c r="E159">
+        <f>COUNTIF('Cook log'!C2:C1000,A159)</f>
+        <v/>
+      </c>
+      <c r="F159" t="n">
+        <v>21</v>
+      </c>
+      <c r="G159">
+        <f>IF(C159="","Never cooked",IF(D159&lt;F159,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Hot and sour soup</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Soup</t>
+        </is>
+      </c>
+      <c r="C160">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A160)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A160)),"")</f>
+        <v/>
+      </c>
+      <c r="D160">
+        <f>IF(C160="","",TODAY()-C160)</f>
+        <v/>
+      </c>
+      <c r="E160">
+        <f>COUNTIF('Cook log'!C2:C1000,A160)</f>
+        <v/>
+      </c>
+      <c r="F160" t="n">
+        <v>21</v>
+      </c>
+      <c r="G160">
+        <f>IF(C160="","Never cooked",IF(D160&lt;F160,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Chicken tsukune</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="C161">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A161)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A161)),"")</f>
+        <v/>
+      </c>
+      <c r="D161">
+        <f>IF(C161="","",TODAY()-C161)</f>
+        <v/>
+      </c>
+      <c r="E161">
+        <f>COUNTIF('Cook log'!C2:C1000,A161)</f>
+        <v/>
+      </c>
+      <c r="F161" t="n">
+        <v>21</v>
+      </c>
+      <c r="G161">
+        <f>IF(C161="","Never cooked",IF(D161&lt;F161,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Sticky honey pork</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C162">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A162)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A162)),"")</f>
+        <v/>
+      </c>
+      <c r="D162">
+        <f>IF(C162="","",TODAY()-C162)</f>
+        <v/>
+      </c>
+      <c r="E162">
+        <f>COUNTIF('Cook log'!C2:C1000,A162)</f>
+        <v/>
+      </c>
+      <c r="F162" t="n">
+        <v>21</v>
+      </c>
+      <c r="G162">
+        <f>IF(C162="","Never cooked",IF(D162&lt;F162,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Chicken rendang</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="C163">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A163)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A163)),"")</f>
+        <v/>
+      </c>
+      <c r="D163">
+        <f>IF(C163="","",TODAY()-C163)</f>
+        <v/>
+      </c>
+      <c r="E163">
+        <f>COUNTIF('Cook log'!C2:C1000,A163)</f>
+        <v/>
+      </c>
+      <c r="F163" t="n">
+        <v>28</v>
+      </c>
+      <c r="G163">
+        <f>IF(C163="","Never cooked",IF(D163&lt;F163,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Steamed stuffed tofu puffs</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C164">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A164)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A164)),"")</f>
+        <v/>
+      </c>
+      <c r="D164">
+        <f>IF(C164="","",TODAY()-C164)</f>
+        <v/>
+      </c>
+      <c r="E164">
+        <f>COUNTIF('Cook log'!C2:C1000,A164)</f>
+        <v/>
+      </c>
+      <c r="F164" t="n">
+        <v>21</v>
+      </c>
+      <c r="G164">
+        <f>IF(C164="","Never cooked",IF(D164&lt;F164,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Lotus leaf rice</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C165">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A165)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A165)),"")</f>
+        <v/>
+      </c>
+      <c r="D165">
+        <f>IF(C165="","",TODAY()-C165)</f>
+        <v/>
+      </c>
+      <c r="E165">
+        <f>COUNTIF('Cook log'!C2:C1000,A165)</f>
+        <v/>
+      </c>
+      <c r="F165" t="n">
+        <v>28</v>
+      </c>
+      <c r="G165">
+        <f>IF(C165="","Never cooked",IF(D165&lt;F165,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Teochew braised duck</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C166">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A166)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A166)),"")</f>
+        <v/>
+      </c>
+      <c r="D166">
+        <f>IF(C166="","",TODAY()-C166)</f>
+        <v/>
+      </c>
+      <c r="E166">
+        <f>COUNTIF('Cook log'!C2:C1000,A166)</f>
+        <v/>
+      </c>
+      <c r="F166" t="n">
+        <v>35</v>
+      </c>
+      <c r="G166">
+        <f>IF(C166="","Never cooked",IF(D166&lt;F166,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Whole duck; elaborate braise</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Mei cai kou rou (Cantonese style)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C167">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A167)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A167)),"")</f>
+        <v/>
+      </c>
+      <c r="D167">
+        <f>IF(C167="","",TODAY()-C167)</f>
+        <v/>
+      </c>
+      <c r="E167">
+        <f>COUNTIF('Cook log'!C2:C1000,A167)</f>
+        <v/>
+      </c>
+      <c r="F167" t="n">
+        <v>28</v>
+      </c>
+      <c r="G167">
+        <f>IF(C167="","Never cooked",IF(D167&lt;F167,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Steamed 1.5-2 hr; see also Hakka version</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Hakka mei cai kou rou</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C168">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A168)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A168)),"")</f>
+        <v/>
+      </c>
+      <c r="D168">
+        <f>IF(C168="","",TODAY()-C168)</f>
+        <v/>
+      </c>
+      <c r="E168">
+        <f>COUNTIF('Cook log'!C2:C1000,A168)</f>
+        <v/>
+      </c>
+      <c r="F168" t="n">
+        <v>28</v>
+      </c>
+      <c r="G168">
+        <f>IF(C168="","Never cooked",IF(D168&lt;F168,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Poach-poke-fry skin; near-duplicate of Mei cai kou rou (Cantonese) - do not schedule both in the same month</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Winter melon bamboo shoot ham soup</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Soup</t>
+        </is>
+      </c>
+      <c r="C169">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A169)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A169)),"")</f>
+        <v/>
+      </c>
+      <c r="D169">
+        <f>IF(C169="","",TODAY()-C169)</f>
+        <v/>
+      </c>
+      <c r="E169">
+        <f>COUNTIF('Cook log'!C2:C1000,A169)</f>
+        <v/>
+      </c>
+      <c r="F169" t="n">
+        <v>21</v>
+      </c>
+      <c r="G169">
+        <f>IF(C169="","Never cooked",IF(D169&lt;F169,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Soak dried bamboo shoots overnight</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Beef rendang</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="C170">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A170)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A170)),"")</f>
+        <v/>
+      </c>
+      <c r="D170">
+        <f>IF(C170="","",TODAY()-C170)</f>
+        <v/>
+      </c>
+      <c r="E170">
+        <f>COUNTIF('Cook log'!C2:C1000,A170)</f>
+        <v/>
+      </c>
+      <c r="F170" t="n">
+        <v>28</v>
+      </c>
+      <c r="G170">
+        <f>IF(C170="","Never cooked",IF(D170&lt;F170,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Madam Kwan's paste version; 50 min simmer. Scratch rempah version = Chicken rendang recipe</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -3562,101 +3562,269 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n"/>
+      <c r="A161" s="2" t="n">
+        <v>46245</v>
+      </c>
       <c r="B161" s="3">
         <f>IF(A161="","",TEXT(A161,"ddd"))</f>
         <v/>
       </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>HK-style steamed chicken</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n"/>
+      <c r="A162" s="2" t="n">
+        <v>46245</v>
+      </c>
       <c r="B162" s="3">
         <f>IF(A162="","",TEXT(A162,"ddd"))</f>
         <v/>
       </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Braised mushrooms with spinach</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n"/>
+      <c r="A163" s="2" t="n">
+        <v>46245</v>
+      </c>
       <c r="B163" s="3">
         <f>IF(A163="","",TEXT(A163,"ddd"))</f>
         <v/>
       </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Radish pork rib soup with dates</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n"/>
+      <c r="A164" s="2" t="n">
+        <v>46245</v>
+      </c>
       <c r="B164" s="3">
         <f>IF(A164="","",TEXT(A164,"ddd"))</f>
         <v/>
       </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n"/>
+      <c r="A165" s="2" t="n">
+        <v>46246</v>
+      </c>
       <c r="B165" s="3">
         <f>IF(A165="","",TEXT(A165,"ddd"))</f>
         <v/>
       </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Yang Zhou fried rice</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026) - EARLY - 12d after 31 Jul, cd 28; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n"/>
+      <c r="A166" s="2" t="n">
+        <v>46246</v>
+      </c>
       <c r="B166" s="3">
         <f>IF(A166="","",TEXT(A166,"ddd"))</f>
         <v/>
       </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Cereal pork chop</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n"/>
+      <c r="A167" s="2" t="n">
+        <v>46246</v>
+      </c>
       <c r="B167" s="3">
         <f>IF(A167="","",TEXT(A167,"ddd"))</f>
         <v/>
       </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n"/>
+      <c r="A168" s="2" t="n">
+        <v>46247</v>
+      </c>
       <c r="B168" s="3">
         <f>IF(A168="","",TEXT(A168,"ddd"))</f>
         <v/>
       </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Steamed baby threadfin</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n"/>
+      <c r="A169" s="2" t="n">
+        <v>46247</v>
+      </c>
       <c r="B169" s="3">
         <f>IF(A169="","",TEXT(A169,"ddd"))</f>
         <v/>
       </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n"/>
+      <c r="A170" s="2" t="n">
+        <v>46247</v>
+      </c>
       <c r="B170" s="3">
         <f>IF(A170="","",TEXT(A170,"ddd"))</f>
         <v/>
       </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Braised pork ribs</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026) - cut the 1 cup rice wine</t>
+        </is>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n"/>
+      <c r="A171" s="2" t="n">
+        <v>46248</v>
+      </c>
       <c r="B171" s="3">
         <f>IF(A171="","",TEXT(A171,"ddd"))</f>
         <v/>
       </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Sticky honey pork</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n"/>
+      <c r="A172" s="2" t="n">
+        <v>46248</v>
+      </c>
       <c r="B172" s="3">
         <f>IF(A172="","",TEXT(A172,"ddd"))</f>
         <v/>
       </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Hainanese chap chye</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n"/>
+      <c r="A173" s="2" t="n">
+        <v>46248</v>
+      </c>
       <c r="B173" s="3">
         <f>IF(A173="","",TEXT(A173,"ddd"))</f>
         <v/>
       </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Tonjiru</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n"/>
+      <c r="A174" s="2" t="n">
+        <v>46248</v>
+      </c>
       <c r="B174" s="3">
         <f>IF(A174="","",TEXT(A174,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>planned (week of 10 Aug 2026)</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -4558,7 +4726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H170"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6413,7 +6581,11 @@
         <f>IF(C58="","Never cooked",IF(D58&lt;F58,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Recipe file deleted - had no quantities or servings. Re-add from https://www.youtube.com/watch?v=aMD3MLJRV38</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -9772,6 +9944,150 @@
       <c r="H170" t="inlineStr">
         <is>
           <t>Madam Kwan's paste version; 50 min simmer. Scratch rempah version = Chicken rendang recipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Cereal pork chop</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C171">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A171)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A171)),"")</f>
+        <v/>
+      </c>
+      <c r="D171">
+        <f>IF(C171="","",TODAY()-C171)</f>
+        <v/>
+      </c>
+      <c r="E171">
+        <f>COUNTIF('Cook log'!C2:C1000,A171)</f>
+        <v/>
+      </c>
+      <c r="F171" t="n">
+        <v>21</v>
+      </c>
+      <c r="G171">
+        <f>IF(C171="","Never cooked",IF(D171&lt;F171,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Deep-fried; toss in buttery cereal</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Braised pork ribs</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C172">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A172)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A172)),"")</f>
+        <v/>
+      </c>
+      <c r="D172">
+        <f>IF(C172="","",TODAY()-C172)</f>
+        <v/>
+      </c>
+      <c r="E172">
+        <f>COUNTIF('Cook log'!C2:C1000,A172)</f>
+        <v/>
+      </c>
+      <c r="F172" t="n">
+        <v>21</v>
+      </c>
+      <c r="G172">
+        <f>IF(C172="","Never cooked",IF(D172&lt;F172,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>1 cup rice wine - long braise</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Pork krapow (Pad Kra Pao)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="C173">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A173)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A173)),"")</f>
+        <v/>
+      </c>
+      <c r="D173">
+        <f>IF(C173="","",TODAY()-C173)</f>
+        <v/>
+      </c>
+      <c r="E173">
+        <f>COUNTIF('Cook log'!C2:C1000,A173)</f>
+        <v/>
+      </c>
+      <c r="F173" t="n">
+        <v>21</v>
+      </c>
+      <c r="G173">
+        <f>IF(C173="","Never cooked",IF(D173&lt;F173,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Thai holy basil stir-fry; recipe written for chicken, pork works</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Braised mushrooms with spinach</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C174">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A174)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A174)),"")</f>
+        <v/>
+      </c>
+      <c r="D174">
+        <f>IF(C174="","",TODAY()-C174)</f>
+        <v/>
+      </c>
+      <c r="E174">
+        <f>COUNTIF('Cook log'!C2:C1000,A174)</f>
+        <v/>
+      </c>
+      <c r="F174" t="n">
+        <v>21</v>
+      </c>
+      <c r="G174">
+        <f>IF(C174="","Never cooked",IF(D174&lt;F174,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>recipes/braised-mushrooms-spinach.md - recipe existed with no rotation row</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -3828,115 +3828,307 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n"/>
+      <c r="A175" s="2" t="n">
+        <v>46251</v>
+      </c>
       <c r="B175" s="3">
         <f>IF(A175="","",TEXT(A175,"ddd"))</f>
         <v/>
       </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pork krapow (Pad Kra Pao)</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - no chilli in a split-off portion for the kid</t>
+        </is>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n"/>
+      <c r="A176" s="2" t="n">
+        <v>46251</v>
+      </c>
       <c r="B176" s="3">
         <f>IF(A176="","",TEXT(A176,"ddd"))</f>
         <v/>
       </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Crispy fried tofu with meat floss</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - omit sesame oil; chicken stock powder for mushroom granules</t>
+        </is>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n"/>
+      <c r="A177" s="2" t="n">
+        <v>46251</v>
+      </c>
       <c r="B177" s="3">
         <f>IF(A177="","",TEXT(A177,"ddd"))</f>
         <v/>
       </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n"/>
+      <c r="A178" s="2" t="n">
+        <v>46251</v>
+      </c>
       <c r="B178" s="3">
         <f>IF(A178="","",TEXT(A178,"ddd"))</f>
         <v/>
       </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n"/>
+      <c r="A179" s="2" t="n">
+        <v>46252</v>
+      </c>
       <c r="B179" s="3">
         <f>IF(A179="","",TEXT(A179,"ddd"))</f>
         <v/>
       </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Pan-fried threadfin with leek</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n"/>
+      <c r="A180" s="2" t="n">
+        <v>46252</v>
+      </c>
       <c r="B180" s="3">
         <f>IF(A180="","",TEXT(A180,"ddd"))</f>
         <v/>
       </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tofu with preserved vegetable</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n"/>
+      <c r="A181" s="2" t="n">
+        <v>46252</v>
+      </c>
       <c r="B181" s="3">
         <f>IF(A181="","",TEXT(A181,"ddd"))</f>
         <v/>
       </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Lotus root pork rib soup</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - EARLY - 14d after 4 Aug, cd 21; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n"/>
+      <c r="A182" s="2" t="n">
+        <v>46252</v>
+      </c>
       <c r="B182" s="3">
         <f>IF(A182="","",TEXT(A182,"ddd"))</f>
         <v/>
       </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n"/>
+      <c r="A183" s="2" t="n">
+        <v>46253</v>
+      </c>
       <c r="B183" s="3">
         <f>IF(A183="","",TEXT(A183,"ddd"))</f>
         <v/>
       </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Braised pork with tofu and egg (Tau Yu Bak)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - eggs kept</t>
+        </is>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n"/>
+      <c r="A184" s="2" t="n">
+        <v>46253</v>
+      </c>
       <c r="B184" s="3">
         <f>IF(A184="","",TEXT(A184,"ddd"))</f>
         <v/>
       </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - hardy green</t>
+        </is>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n"/>
+      <c r="A185" s="2" t="n">
+        <v>46253</v>
+      </c>
       <c r="B185" s="3">
         <f>IF(A185="","",TEXT(A185,"ddd"))</f>
         <v/>
       </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Chinese yam and chicken soup</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - PORK RIB version; EARLY - 14d after 5 Aug, cd 21; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n"/>
+      <c r="A186" s="2" t="n">
+        <v>46253</v>
+      </c>
       <c r="B186" s="3">
         <f>IF(A186="","",TEXT(A186,"ddd"))</f>
         <v/>
       </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n"/>
+      <c r="A187" s="2" t="n">
+        <v>46254</v>
+      </c>
       <c r="B187" s="3">
         <f>IF(A187="","",TEXT(A187,"ddd"))</f>
         <v/>
       </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Fried chicken wings</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n"/>
+      <c r="A188" s="2" t="n">
+        <v>46254</v>
+      </c>
       <c r="B188" s="3">
         <f>IF(A188="","",TEXT(A188,"ddd"))</f>
         <v/>
       </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Hokkien gai fan</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n"/>
+      <c r="A189" s="2" t="n">
+        <v>46255</v>
+      </c>
       <c r="B189" s="3">
         <f>IF(A189="","",TEXT(A189,"ddd"))</f>
         <v/>
       </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Yang Zhou fried rice</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - EARLY - 9d after 12 Aug, cd 28; 3rd time in 3 weeks; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n"/>
+      <c r="A190" s="2" t="n">
+        <v>46255</v>
+      </c>
       <c r="B190" s="3">
         <f>IF(A190="","",TEXT(A190,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Satay</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>planned (week of 17 Aug 2026) - frozen, using up</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -4726,7 +4918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10088,6 +10280,186 @@
       <c r="H174" t="inlineStr">
         <is>
           <t>recipes/braised-mushrooms-spinach.md - recipe existed with no rotation row</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Crispy fried tofu with meat floss</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C175">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A175)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A175)),"")</f>
+        <v/>
+      </c>
+      <c r="D175">
+        <f>IF(C175="","",TODAY()-C175)</f>
+        <v/>
+      </c>
+      <c r="E175">
+        <f>COUNTIF('Cook log'!C2:C1000,A175)</f>
+        <v/>
+      </c>
+      <c r="F175" t="n">
+        <v>21</v>
+      </c>
+      <c r="G175">
+        <f>IF(C175="","Never cooked",IF(D175&lt;F175,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Omit sesame oil; sub chicken stock powder for mushroom granules</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Pan-fried threadfin with leek</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="C176">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A176)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A176)),"")</f>
+        <v/>
+      </c>
+      <c r="D176">
+        <f>IF(C176="","",TODAY()-C176)</f>
+        <v/>
+      </c>
+      <c r="E176">
+        <f>COUNTIF('Cook log'!C2:C1000,A176)</f>
+        <v/>
+      </c>
+      <c r="F176" t="n">
+        <v>21</v>
+      </c>
+      <c r="G176">
+        <f>IF(C176="","Never cooked",IF(D176&lt;F176,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Household - Mia improvises</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Tofu with preserved vegetable</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="C177">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A177)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A177)),"")</f>
+        <v/>
+      </c>
+      <c r="D177">
+        <f>IF(C177="","",TODAY()-C177)</f>
+        <v/>
+      </c>
+      <c r="E177">
+        <f>COUNTIF('Cook log'!C2:C1000,A177)</f>
+        <v/>
+      </c>
+      <c r="F177" t="n">
+        <v>21</v>
+      </c>
+      <c r="G177">
+        <f>IF(C177="","Never cooked",IF(D177&lt;F177,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Household - chai poh tofu; rinse the preserved veg well</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Hokkien gai fan</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="C178">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A178)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A178)),"")</f>
+        <v/>
+      </c>
+      <c r="D178">
+        <f>IF(C178="","",TODAY()-C178)</f>
+        <v/>
+      </c>
+      <c r="E178">
+        <f>COUNTIF('Cook log'!C2:C1000,A178)</f>
+        <v/>
+      </c>
+      <c r="F178" t="n">
+        <v>21</v>
+      </c>
+      <c r="G178">
+        <f>IF(C178="","Never cooked",IF(D178&lt;F178,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Household - Mia knows it</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Satay</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C179">
+        <f>IFERROR(IF(MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A179)=0,"",MAXIFS('Cook log'!A2:A1000,'Cook log'!C2:C1000,A179)),"")</f>
+        <v/>
+      </c>
+      <c r="D179">
+        <f>IF(C179="","",TODAY()-C179)</f>
+        <v/>
+      </c>
+      <c r="E179">
+        <f>COUNTIF('Cook log'!C2:C1000,A179)</f>
+        <v/>
+      </c>
+      <c r="F179" t="n">
+        <v>28</v>
+      </c>
+      <c r="G179">
+        <f>IF(C179="","Never cooked",IF(D179&lt;F179,"Cooldown","Due"))</f>
+        <v/>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Usually bought/frozen; reheat through</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +104,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4132,206 +4133,554 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n"/>
+      <c r="A191" s="8" t="n">
+        <v>46272</v>
+      </c>
       <c r="B191" s="3">
         <f>IF(A191="","",TEXT(A191,"ddd"))</f>
         <v/>
       </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried bee hoon</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n"/>
+      <c r="A192" s="8" t="n">
+        <v>46272</v>
+      </c>
       <c r="B192" s="3">
         <f>IF(A192="","",TEXT(A192,"ddd"))</f>
         <v/>
       </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>Watercress pork rib soup</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - 1kg ribs across 4 soups this week, reduced by user</t>
+        </is>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n"/>
+      <c r="A193" s="8" t="n">
+        <v>46273</v>
+      </c>
       <c r="B193" s="3">
         <f>IF(A193="","",TEXT(A193,"ddd"))</f>
         <v/>
       </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>Steamed baby threadfin</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - no recipe file; quantities invented</t>
+        </is>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n"/>
+      <c r="A194" s="8" t="n">
+        <v>46273</v>
+      </c>
       <c r="B194" s="3">
         <f>IF(A194="","",TEXT(A194,"ddd"))</f>
         <v/>
       </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried dou miao</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n"/>
+      <c r="A195" s="8" t="n">
+        <v>46273</v>
+      </c>
       <c r="B195" s="3">
         <f>IF(A195="","",TEXT(A195,"ddd"))</f>
         <v/>
       </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>Chinese yam and chicken soup</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - PORK RIB version; EARLY - 20d after 19 Aug, cd 21; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n"/>
+      <c r="A196" s="8" t="n">
+        <v>46273</v>
+      </c>
       <c r="B196" s="3">
         <f>IF(A196="","",TEXT(A196,"ddd"))</f>
         <v/>
       </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n"/>
+      <c r="A197" s="8" t="n">
+        <v>46274</v>
+      </c>
       <c r="B197" s="3">
         <f>IF(A197="","",TEXT(A197,"ddd"))</f>
         <v/>
       </c>
+      <c r="C197" s="3" t="inlineStr">
+        <is>
+          <t>Yang Zhou fried rice</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - EARLY - 19d after 21 Aug, cd 28; user approved; sesame oil -&gt; neutral</t>
+        </is>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n"/>
+      <c r="A198" s="8" t="n">
+        <v>46274</v>
+      </c>
       <c r="B198" s="3">
         <f>IF(A198="","",TEXT(A198,"ddd"))</f>
         <v/>
       </c>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Fishball minced pork soup</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - recipe has no quantities; invented</t>
+        </is>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n"/>
+      <c r="A199" s="8" t="n">
+        <v>46275</v>
+      </c>
       <c r="B199" s="3">
         <f>IF(A199="","",TEXT(A199,"ddd"))</f>
         <v/>
       </c>
+      <c r="C199" s="3" t="inlineStr">
+        <is>
+          <t>Baked salmon with herbs</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n"/>
+      <c r="A200" s="8" t="n">
+        <v>46275</v>
+      </c>
       <c r="B200" s="3">
         <f>IF(A200="","",TEXT(A200,"ddd"))</f>
         <v/>
       </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - soft green, day 4</t>
+        </is>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n"/>
+      <c r="A201" s="8" t="n">
+        <v>46275</v>
+      </c>
       <c r="B201" s="3">
         <f>IF(A201="","",TEXT(A201,"ddd"))</f>
         <v/>
       </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
+          <t>Lotus root pork rib soup</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - recipe serves 12; HALF batch</t>
+        </is>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
+      <c r="A202" s="8" t="n">
+        <v>46275</v>
+      </c>
       <c r="B202" s="3">
         <f>IF(A202="","",TEXT(A202,"ddd"))</f>
         <v/>
       </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n"/>
+      <c r="A203" s="8" t="n">
+        <v>46276</v>
+      </c>
       <c r="B203" s="3">
         <f>IF(A203="","",TEXT(A203,"ddd"))</f>
         <v/>
       </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Ee-fu mee</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - mushrooms KEPT by user override; SLICED PORK 400g not chicken thigh</t>
+        </is>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n"/>
+      <c r="A204" s="8" t="n">
+        <v>46276</v>
+      </c>
       <c r="B204" s="3">
         <f>IF(A204="","",TEXT(A204,"ddd"))</f>
         <v/>
       </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Radish pork rib soup with dates</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n"/>
+      <c r="A205" s="8" t="n">
+        <v>46276</v>
+      </c>
       <c r="B205" s="3">
         <f>IF(A205="","",TEXT(A205,"ddd"))</f>
         <v/>
       </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 7 Sep 2026) - hardy green (kai lan), day 5</t>
+        </is>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n"/>
+      <c r="A206" s="8" t="n">
+        <v>46279</v>
+      </c>
       <c r="B206" s="3">
         <f>IF(A206="","",TEXT(A206,"ddd"))</f>
         <v/>
       </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Buta don 豚丼</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - raw egg yolk topping OMITTED; alcohol override</t>
+        </is>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n"/>
+      <c r="A207" s="8" t="n">
+        <v>46279</v>
+      </c>
       <c r="B207" s="3">
         <f>IF(A207="","",TEXT(A207,"ddd"))</f>
         <v/>
       </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Watercress pork rib soup</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - EARLY: 7d after 7 Sep, cd 21; user chose 12 Sep</t>
+        </is>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n"/>
+      <c r="A208" s="8" t="n">
+        <v>46280</v>
+      </c>
       <c r="B208" s="3">
         <f>IF(A208="","",TEXT(A208,"ddd"))</f>
         <v/>
       </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Taiwanese beef noodle soup 红烧牛肉面</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - tomato + alcohol override; CHILD: ladle before the chilli</t>
+        </is>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n"/>
+      <c r="A209" s="8" t="n">
+        <v>46281</v>
+      </c>
       <c r="B209" s="3">
         <f>IF(A209="","",TEXT(A209,"ddd"))</f>
         <v/>
       </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Padang chicken curry</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - 2 packets Dancing Chef paste</t>
+        </is>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n"/>
+      <c r="A210" s="8" t="n">
+        <v>46281</v>
+      </c>
       <c r="B210" s="3">
         <f>IF(A210="","",TEXT(A210,"ddd"))</f>
         <v/>
       </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Fishball and baby spinach soup</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - no recipe; quantities invented</t>
+        </is>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n"/>
+      <c r="A211" s="8" t="n">
+        <v>46282</v>
+      </c>
       <c r="B211" s="3">
         <f>IF(A211="","",TEXT(A211,"ddd"))</f>
         <v/>
       </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Steamed pomfret</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - no recipe; quantities invented</t>
+        </is>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n"/>
+      <c r="A212" s="8" t="n">
+        <v>46282</v>
+      </c>
       <c r="B212" s="3">
         <f>IF(A212="","",TEXT(A212,"ddd"))</f>
         <v/>
       </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Braised meatballs in oyster sauce 蚝油焖肉丸</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - FIRST COOK; minced PORK (recipe default)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n"/>
+      <c r="A213" s="8" t="n">
+        <v>46282</v>
+      </c>
       <c r="B213" s="3">
         <f>IF(A213="","",TEXT(A213,"ddd"))</f>
         <v/>
       </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - soft green, day 4</t>
+        </is>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n"/>
+      <c r="A214" s="8" t="n">
+        <v>46282</v>
+      </c>
       <c r="B214" s="3">
         <f>IF(A214="","",TEXT(A214,"ddd"))</f>
         <v/>
       </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Tonjiru</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n"/>
+      <c r="A215" s="8" t="n">
+        <v>46282</v>
+      </c>
       <c r="B215" s="3">
         <f>IF(A215="","",TEXT(A215,"ddd"))</f>
         <v/>
       </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n"/>
+      <c r="A216" s="8" t="n">
+        <v>46283</v>
+      </c>
       <c r="B216" s="3">
         <f>IF(A216="","",TEXT(A216,"ddd"))</f>
         <v/>
       </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Pan-fried threadfin with leek</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - no recipe; freeze Sun, thaw Thu night</t>
+        </is>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n"/>
+      <c r="A217" s="8" t="n">
+        <v>46283</v>
+      </c>
       <c r="B217" s="3">
         <f>IF(A217="","",TEXT(A217,"ddd"))</f>
         <v/>
       </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Sweet and sour pork</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - tomato override; sesame oil DELETED; pork raised to 600g</t>
+        </is>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n"/>
+      <c r="A218" s="8" t="n">
+        <v>46283</v>
+      </c>
       <c r="B218" s="3">
         <f>IF(A218="","",TEXT(A218,"ddd"))</f>
         <v/>
       </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026) - hardy green, day 5</t>
+        </is>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n"/>
+      <c r="A219" s="8" t="n">
+        <v>46283</v>
+      </c>
       <c r="B219" s="3">
         <f>IF(A219="","",TEXT(A219,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 14 Sep 2026)</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -4918,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10460,6 +10809,66 @@
       <c r="H179" t="inlineStr">
         <is>
           <t>Usually bought/frozen; reheat through</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Braised meatballs in oyster sauce 蚝油焖肉丸</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>recipes/braised-meatballs-oyster-sauce.md - prawn+pork meatballs, braised. Recipe serves 3-4. Clean: no tomato/sesame/mushroom/wine</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Buta don 豚丼</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H181" s="3" t="inlineStr">
+        <is>
+          <t>recipes/buta-don.md - recipe PRE-SCALED to 6.5 pax. 195ml sake + 195ml mirin; optional raw yolks MUST be omitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Taiwanese beef noodle soup 红烧牛肉面</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>Noodle</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H182" s="3" t="inlineStr">
+        <is>
+          <t>recipes/taiwanese-beef-noodle-soup.md - PRE-SCALED to 6.5 pax. Tomato + doubanjiang base; spicy, no child dish if served alone</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cook log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dish rotation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cook log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dish rotation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cook log'!$A$1:$D$300</definedName>
@@ -5267,7 +5267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10869,6 +10869,86 @@
       <c r="H182" s="3" t="inlineStr">
         <is>
           <t>recipes/taiwanese-beef-noodle-soup.md - PRE-SCALED to 6.5 pax. Tomato + doubanjiang base; spicy, no child dish if served alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Chicken parm sandwich</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H183" s="3" t="inlineStr">
+        <is>
+          <t>recipes/chicken-parm-sandwich.md - vodka sauce, tomato now OK. Chilli flakes marked optional - omit for child</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Balinese braised beef</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H184" s="3" t="inlineStr">
+        <is>
+          <t>recipes/balinese-braised-beef.md - mild chilli flakes 1/2 tsp; elaborate-ish braise</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Curry fish head 咖喱鱼头</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>recipes/curry-fish-head.md - using fish FILLET not head. Nyonya rempah, tomato+eggplant+long beans+okra. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>Braised duck (Ah Gong's recipe) 卤鸭</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H186" s="3" t="inlineStr">
+        <is>
+          <t>recipes/braised-duck-ah-gong-recipe.md - Fully confirmed via Ah Gong's own WhatsApp messages. Separate rotation entry so it doesn't collide with the Teochew version. Never cooked.</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cook log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dish rotation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cook log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dish rotation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cook log'!$A$1:$D$300</definedName>
@@ -4684,108 +4684,288 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n"/>
+      <c r="A220" s="8" t="n">
+        <v>46285</v>
+      </c>
       <c r="B220" s="3">
         <f>IF(A220="","",TEXT(A220,"ddd"))</f>
         <v/>
       </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Curry fish head 咖喱鱼头</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 21 Sep 2026) - fish FILLET not head</t>
+        </is>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n"/>
+      <c r="A221" s="8" t="n">
+        <v>46286</v>
+      </c>
       <c r="B221" s="3">
         <f>IF(A221="","",TEXT(A221,"ddd"))</f>
         <v/>
       </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Chicken parm sandwich</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - served as CUTLETS, no sandwich, half breast each; chilli flakes omitted</t>
+        </is>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n"/>
+      <c r="A222" s="8" t="n">
+        <v>46286</v>
+      </c>
       <c r="B222" s="3">
         <f>IF(A222="","",TEXT(A222,"ddd"))</f>
         <v/>
       </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Mushroom soup</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n"/>
+      <c r="A223" s="8" t="n">
+        <v>46286</v>
+      </c>
       <c r="B223" s="3">
         <f>IF(A223="","",TEXT(A223,"ddd"))</f>
         <v/>
       </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>Roasted vegetables (oven)</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - basil folded in hot</t>
+        </is>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n"/>
+      <c r="A224" s="8" t="n">
+        <v>46287</v>
+      </c>
       <c r="B224" s="3">
         <f>IF(A224="","",TEXT(A224,"ddd"))</f>
         <v/>
       </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>Teochew braised duck</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - per week file; Ah Gong version was being developed same week, confirm which was actually cooked</t>
+        </is>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n"/>
+      <c r="A225" s="8" t="n">
+        <v>46287</v>
+      </c>
       <c r="B225" s="3">
         <f>IF(A225="","",TEXT(A225,"ddd"))</f>
         <v/>
       </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n"/>
+      <c r="A226" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="B226" s="3">
         <f>IF(A226="","",TEXT(A226,"ddd"))</f>
         <v/>
       </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Kong bak pau (braised pork buns)</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - frozen mantou; scaled down from 25 servings</t>
+        </is>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n"/>
+      <c r="A227" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="B227" s="3">
         <f>IF(A227="","",TEXT(A227,"ddd"))</f>
         <v/>
       </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried dou miao</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n"/>
+      <c r="A228" s="8" t="n">
+        <v>46288</v>
+      </c>
       <c r="B228" s="3">
         <f>IF(A228="","",TEXT(A228,"ddd"))</f>
         <v/>
       </c>
+      <c r="C228" s="3" t="inlineStr">
+        <is>
+          <t>Hot and sour soup</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n"/>
+      <c r="A229" s="8" t="n">
+        <v>46289</v>
+      </c>
       <c r="B229" s="3">
         <f>IF(A229="","",TEXT(A229,"ddd"))</f>
         <v/>
       </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>Balinese braised beef</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - FIRST COOK</t>
+        </is>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n"/>
+      <c r="A230" s="8" t="n">
+        <v>46289</v>
+      </c>
       <c r="B230" s="3">
         <f>IF(A230="","",TEXT(A230,"ddd"))</f>
         <v/>
       </c>
+      <c r="C230" s="3" t="inlineStr">
+        <is>
+          <t>Hainanese chap chye</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n"/>
+      <c r="A231" s="8" t="n">
+        <v>46289</v>
+      </c>
       <c r="B231" s="3">
         <f>IF(A231="","",TEXT(A231,"ddd"))</f>
         <v/>
       </c>
+      <c r="C231" s="3" t="inlineStr">
+        <is>
+          <t>Chinese yam and chicken soup</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - PORK RIB version; EARLY 16d after 8 Sep, cd 21; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n"/>
+      <c r="A232" s="8" t="n">
+        <v>46290</v>
+      </c>
       <c r="B232" s="3">
         <f>IF(A232="","",TEXT(A232,"ddd"))</f>
         <v/>
       </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>Taiwanese fried rice</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n"/>
+      <c r="A233" s="8" t="n">
+        <v>46290</v>
+      </c>
       <c r="B233" s="3">
         <f>IF(A233="","",TEXT(A233,"ddd"))</f>
         <v/>
       </c>
+      <c r="C233" s="3" t="inlineStr">
+        <is>
+          <t>Wasabi mayo prawns</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - Kewpie mayo instead of from-scratch</t>
+        </is>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n"/>
+      <c r="A234" s="8" t="n">
+        <v>46290</v>
+      </c>
       <c r="B234" s="3">
         <f>IF(A234="","",TEXT(A234,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Radish pork rib soup with dates</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 21 Sep 2026) - EARLY 14d after 11 Sep, cd 21; user approved</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -5267,7 +5447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7090,7 +7270,11 @@
         <f>IF(C57="","Never cooked",IF(D57&lt;F57,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>recipes/hey-zho.md - makes 13 rolls / 39 pieces; steamed 15 min, cooled, cornflour-coated, deep-fried. Needs 1kg peeled prawns, 5-spice beancurd skin. Never cooked</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -10949,6 +11133,66 @@
       <c r="H186" s="3" t="inlineStr">
         <is>
           <t>recipes/braised-duck-ah-gong-recipe.md - Fully confirmed via Ah Gong's own WhatsApp messages. Separate rotation entry so it doesn't collide with the Teochew version. Never cooked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>Pan-fried salmon</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H187" s="3" t="inlineStr">
+        <is>
+          <t>Household - no recipe file; added 24 Sep. Fully cook through</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>Braised oxtail (Hainanese style)</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H188" s="3" t="inlineStr">
+        <is>
+          <t>recipes/hainanese-oxtail-stew.md - Meatmen Channel; 2hr braise, oxtail floured+fried first. Serves 4-6 on 2kg. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Braised oxtail (red wine)</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H189" s="3" t="inlineStr">
+        <is>
+          <t>recipes/red-wine-braised-oxtail.md - West Country Kitchen; oven braise 4-5hr at 140-150C, served on mash. Serves 3-4, oxtail weight not stated. Never cooked</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -4969,115 +4969,307 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n"/>
+      <c r="A235" s="8" t="n">
+        <v>46292</v>
+      </c>
       <c r="B235" s="3">
         <f>IF(A235="","",TEXT(A235,"ddd"))</f>
         <v/>
       </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Cubano sandwich</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 28 Sep 2026) - FIRST COOK; half batch for 4; marinated Sat night</t>
+        </is>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n"/>
+      <c r="A236" s="8" t="n">
+        <v>46293</v>
+      </c>
       <c r="B236" s="3">
         <f>IF(A236="","",TEXT(A236,"ddd"))</f>
         <v/>
       </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>HK style steamed seabass</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - 2 fish ~600g, steamed one at a time</t>
+        </is>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n"/>
+      <c r="A237" s="8" t="n">
+        <v>46293</v>
+      </c>
       <c r="B237" s="3">
         <f>IF(A237="","",TEXT(A237,"ddd"))</f>
         <v/>
       </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Winter melon pork rib soup</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - no recipe; household</t>
+        </is>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n"/>
+      <c r="A238" s="8" t="n">
+        <v>46293</v>
+      </c>
       <c r="B238" s="3">
         <f>IF(A238="","",TEXT(A238,"ddd"))</f>
         <v/>
       </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n"/>
+      <c r="A239" s="8" t="n">
+        <v>46293</v>
+      </c>
       <c r="B239" s="3">
         <f>IF(A239="","",TEXT(A239,"ddd"))</f>
         <v/>
       </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n"/>
+      <c r="A240" s="8" t="n">
+        <v>46294</v>
+      </c>
       <c r="B240" s="3">
         <f>IF(A240="","",TEXT(A240,"ddd"))</f>
         <v/>
       </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Hey zho (prawn rolls)</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - FIRST COOK; recipes/hey-zho.md, 13 rolls</t>
+        </is>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n"/>
+      <c r="A241" s="8" t="n">
+        <v>46294</v>
+      </c>
       <c r="B241" s="3">
         <f>IF(A241="","",TEXT(A241,"ddd"))</f>
         <v/>
       </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Pan-fried salmon</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - FIRST COOK; no recipe</t>
+        </is>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n"/>
+      <c r="A242" s="8" t="n">
+        <v>46294</v>
+      </c>
       <c r="B242" s="3">
         <f>IF(A242="","",TEXT(A242,"ddd"))</f>
         <v/>
       </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>ABC soup</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - picked by Claude, Tuesday soup was unspecified</t>
+        </is>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n"/>
+      <c r="A243" s="8" t="n">
+        <v>46295</v>
+      </c>
       <c r="B243" s="3">
         <f>IF(A243="","",TEXT(A243,"ddd"))</f>
         <v/>
       </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Cheesy baked rice</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - ESTIMATED recipe, not the family method</t>
+        </is>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n"/>
+      <c r="A244" s="8" t="n">
+        <v>46295</v>
+      </c>
       <c r="B244" s="3">
         <f>IF(A244="","",TEXT(A244,"ddd"))</f>
         <v/>
       </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Campbell's mushroom soup</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n"/>
+      <c r="A245" s="8" t="n">
+        <v>46296</v>
+      </c>
       <c r="B245" s="3">
         <f>IF(A245="","",TEXT(A245,"ddd"))</f>
         <v/>
       </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Braised oxtail (Hainanese style)</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - FIRST COOK; shank if no oxtail</t>
+        </is>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n"/>
+      <c r="A246" s="8" t="n">
+        <v>46296</v>
+      </c>
       <c r="B246" s="3">
         <f>IF(A246="","",TEXT(A246,"ddd"))</f>
         <v/>
       </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Hot and sour soup</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - EARLY 8d after 23 Sep, cd 21; user approved</t>
+        </is>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n"/>
+      <c r="A247" s="8" t="n">
+        <v>46296</v>
+      </c>
       <c r="B247" s="3">
         <f>IF(A247="","",TEXT(A247,"ddd"))</f>
         <v/>
       </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n"/>
+      <c r="A248" s="8" t="n">
+        <v>46296</v>
+      </c>
       <c r="B248" s="3">
         <f>IF(A248="","",TEXT(A248,"ddd"))</f>
         <v/>
       </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n"/>
+      <c r="A249" s="8" t="n">
+        <v>46297</v>
+      </c>
       <c r="B249" s="3">
         <f>IF(A249="","",TEXT(A249,"ddd"))</f>
         <v/>
       </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Pulled pork burger</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - served as SANDWICH on regular bread; no coleslaw</t>
+        </is>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n"/>
+      <c r="A250" s="8" t="n">
+        <v>46297</v>
+      </c>
       <c r="B250" s="3">
         <f>IF(A250="","",TEXT(A250,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Grilled broccoli &amp; carrots</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 28 Sep 2026) - with capsicum</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -5447,7 +5639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7308,7 +7500,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Recipe file deleted - had no quantities or servings. Re-add from https://www.youtube.com/watch?v=aMD3MLJRV38</t>
+          <t>recipes/thai-fish-cakes.md - restored 3 Oct from git (Tod Mun Pla); ingredient list only, NO quantities yet</t>
         </is>
       </c>
     </row>
@@ -11193,6 +11385,66 @@
       <c r="H189" s="3" t="inlineStr">
         <is>
           <t>recipes/red-wine-braised-oxtail.md - West Country Kitchen; oven braise 4-5hr at 140-150C, served on mash. Serves 3-4, oxtail weight not stated. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Hakka yam pork belly 芋头扣肉</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H190" s="3" t="inlineStr">
+        <is>
+          <t>recipes/hakka-yam-pork-belly.md - serves 6-8; marinate 1hr, pan-fry, steam 1.5hr in a rice cooker. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>Stir-fried eggs with Chinese sausage 腊肠炒蛋</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>Egg</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>Household - no recipe file. Eggs cooked firm. Added 3 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Japchae 잡채</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Noodle</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>recipes/japchae.md - serves 3-4 as written (100g noodles, 50g beef). Never cooked</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -5273,94 +5273,250 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n"/>
+      <c r="A251" s="8" t="n">
+        <v>46299</v>
+      </c>
       <c r="B251" s="3">
         <f>IF(A251="","",TEXT(A251,"ddd"))</f>
         <v/>
       </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Japchae 잡채</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 5 Oct 2026) - FIRST COOK; recipes/japchae.md pre-scaled 5.5</t>
+        </is>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n"/>
+      <c r="A252" s="8" t="n">
+        <v>46300</v>
+      </c>
       <c r="B252" s="3">
         <f>IF(A252="","",TEXT(A252,"ddd"))</f>
         <v/>
       </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Hakka yam pork belly 芋头扣肉</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - FIRST COOK; steam Sun night, rice cooker busy Mon</t>
+        </is>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n"/>
+      <c r="A253" s="8" t="n">
+        <v>46300</v>
+      </c>
       <c r="B253" s="3">
         <f>IF(A253="","",TEXT(A253,"ddd"))</f>
         <v/>
       </c>
+      <c r="C253" s="3" t="inlineStr">
+        <is>
+          <t>Stir-fried eggs with Chinese sausage 腊肠炒蛋</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - FIRST COOK; household, no recipe; eggs cooked firm</t>
+        </is>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n"/>
+      <c r="A254" s="8" t="n">
+        <v>46300</v>
+      </c>
       <c r="B254" s="3">
         <f>IF(A254="","",TEXT(A254,"ddd"))</f>
         <v/>
       </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Watercress pork rib soup</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - picked by Claude - Monday soup was "no bamboo shoot"</t>
+        </is>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n"/>
+      <c r="A255" s="8" t="n">
+        <v>46300</v>
+      </c>
       <c r="B255" s="3">
         <f>IF(A255="","",TEXT(A255,"ddd"))</f>
         <v/>
       </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n"/>
+      <c r="A256" s="8" t="n">
+        <v>46301</v>
+      </c>
       <c r="B256" s="3">
         <f>IF(A256="","",TEXT(A256,"ddd"))</f>
         <v/>
       </c>
+      <c r="C256" s="3" t="inlineStr">
+        <is>
+          <t>Steamed baby threadfin</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - picked by Claude for "some steamed fish"</t>
+        </is>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n"/>
+      <c r="A257" s="8" t="n">
+        <v>46301</v>
+      </c>
       <c r="B257" s="3">
         <f>IF(A257="","",TEXT(A257,"ddd"))</f>
         <v/>
       </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Fried chicken wings</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - replaced Thai fishcakes (user, 3 Oct); ~1.6kg wings</t>
+        </is>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n"/>
+      <c r="A258" s="8" t="n">
+        <v>46301</v>
+      </c>
       <c r="B258" s="3">
         <f>IF(A258="","",TEXT(A258,"ddd"))</f>
         <v/>
       </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n"/>
+      <c r="A259" s="8" t="n">
+        <v>46301</v>
+      </c>
       <c r="B259" s="3">
         <f>IF(A259="","",TEXT(A259,"ddd"))</f>
         <v/>
       </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n"/>
+      <c r="A260" s="8" t="n">
+        <v>46302</v>
+      </c>
       <c r="B260" s="3">
         <f>IF(A260="","",TEXT(A260,"ddd"))</f>
         <v/>
       </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Japanese curry rice</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - ~600g chicken (estimate); chilli reduced for the child</t>
+        </is>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n"/>
+      <c r="A261" s="8" t="n">
+        <v>46302</v>
+      </c>
       <c r="B261" s="3">
         <f>IF(A261="","",TEXT(A261,"ddd"))</f>
         <v/>
       </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Fishball soup with cabbage</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - FIRST COOK; picked by Claude; household, no recipe</t>
+        </is>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n"/>
+      <c r="A262" s="8" t="n">
+        <v>46304</v>
+      </c>
       <c r="B262" s="3">
         <f>IF(A262="","",TEXT(A262,"ddd"))</f>
         <v/>
       </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Shepherd's pie</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - lamb ~1kg for 5.5 (or beef)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n"/>
+      <c r="A263" s="8" t="n">
+        <v>46304</v>
+      </c>
       <c r="B263" s="3">
         <f>IF(A263="","",TEXT(A263,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Mushroom soup</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 5 Oct 2026) - EARLY 18d after 21 Sep, cd 28; user approved; no cream this time</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -7500,7 +7656,7 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>recipes/thai-fish-cakes.md - restored 3 Oct from git (Tod Mun Pla); ingredient list only, NO quantities yet</t>
+          <t>recipes/thai-fish-cakes.md - PRE-SCALED to 5.5 pax (x1.6); original video ingredients + user-supplied guide quantities. Deep-fried; spicy (red curry paste)</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11232,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Household - Mia improvises</t>
+          <t>Household - no recipe file. Was Mia's dish; Mia briefed Jayzel on household dishes before leaving 3 Oct 2026 - check Jayzel knows this one</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11304,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Household - Mia knows it</t>
+          <t>Household - no recipe file. Was Mia's dish; Mia briefed Jayzel on household dishes before leaving 3 Oct 2026 - check Jayzel knows this one</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11560,7 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>recipes/hakka-yam-pork-belly.md - serves 6-8; marinate 1hr, pan-fry, steam 1.5hr in a rice cooker. Never cooked</t>
+          <t>recipes/hakka-yam-pork-belly.md - PRE-SCALED to 5.5 pax (x0.8 from source 6-8); marinate 1hr, pan-fry, steam 1.5hr. Never cooked</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11600,7 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>recipes/japchae.md - serves 3-4 as written (100g noodles, 50g beef). Never cooked</t>
+          <t>recipes/japchae.md - PRE-SCALED to 5.5 pax (x1.6 from source 3-4). Side-dish portions: 80g beef. Never cooked</t>
         </is>
       </c>
     </row>

--- a/dish-rotation.xlsx
+++ b/dish-rotation.xlsx
@@ -5520,227 +5520,611 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n"/>
+      <c r="A264" s="8" t="n">
+        <v>46306</v>
+      </c>
       <c r="B264" s="3">
         <f>IF(A264="","",TEXT(A264,"ddd"))</f>
         <v/>
       </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Beef hayashi rice</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 12 Oct 2026) - FIRST COOK; as written</t>
+        </is>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n"/>
+      <c r="A265" s="8" t="n">
+        <v>46307</v>
+      </c>
       <c r="B265" s="3">
         <f>IF(A265="","",TEXT(A265,"ddd"))</f>
         <v/>
       </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>Greek lemon chicken</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - FIRST COOK; the 5 thighs at home; marinade x0.6</t>
+        </is>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n"/>
+      <c r="A266" s="8" t="n">
+        <v>46307</v>
+      </c>
       <c r="B266" s="3">
         <f>IF(A266="","",TEXT(A266,"ddd"))</f>
         <v/>
       </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Crispy roast potatoes</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - recipes/roast-potatoes.md 1.5kg</t>
+        </is>
+      </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n"/>
+      <c r="A267" s="8" t="n">
+        <v>46307</v>
+      </c>
       <c r="B267" s="3">
         <f>IF(A267="","",TEXT(A267,"ddd"))</f>
         <v/>
       </c>
+      <c r="C267" s="3" t="inlineStr">
+        <is>
+          <t>Roasted vegetables (oven)</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - no potato wedges; x1.25</t>
+        </is>
+      </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n"/>
+      <c r="A268" s="8" t="n">
+        <v>46308</v>
+      </c>
       <c r="B268" s="3">
         <f>IF(A268="","",TEXT(A268,"ddd"))</f>
         <v/>
       </c>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Steamed pomfret</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - 2 fish 500-600g, steamed one at a time</t>
+        </is>
+      </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n"/>
+      <c r="A269" s="8" t="n">
+        <v>46308</v>
+      </c>
       <c r="B269" s="3">
         <f>IF(A269="","",TEXT(A269,"ddd"))</f>
         <v/>
       </c>
+      <c r="C269" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried dou miao</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - x2</t>
+        </is>
+      </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n"/>
+      <c r="A270" s="8" t="n">
+        <v>46308</v>
+      </c>
       <c r="B270" s="3">
         <f>IF(A270="","",TEXT(A270,"ddd"))</f>
         <v/>
       </c>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Pork rib king</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - x1.5; method in the video</t>
+        </is>
+      </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n"/>
+      <c r="A271" s="8" t="n">
+        <v>46309</v>
+      </c>
       <c r="B271" s="3">
         <f>IF(A271="","",TEXT(A271,"ddd"))</f>
         <v/>
       </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Chicken curry</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - dried chillies cut to 3-4</t>
+        </is>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n"/>
+      <c r="A272" s="8" t="n">
+        <v>46309</v>
+      </c>
       <c r="B272" s="3">
         <f>IF(A272="","",TEXT(A272,"ddd"))</f>
         <v/>
       </c>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Frozen prata</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - store-bought</t>
+        </is>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n"/>
+      <c r="A273" s="8" t="n">
+        <v>46310</v>
+      </c>
       <c r="B273" s="3">
         <f>IF(A273="","",TEXT(A273,"ddd"))</f>
         <v/>
       </c>
+      <c r="C273" s="3" t="inlineStr">
+        <is>
+          <t>Black pepper beef</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - FIRST COOK; 400g; method inferred</t>
+        </is>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n"/>
+      <c r="A274" s="8" t="n">
+        <v>46310</v>
+      </c>
       <c r="B274" s="3">
         <f>IF(A274="","",TEXT(A274,"ddd"))</f>
         <v/>
       </c>
+      <c r="C274" s="3" t="inlineStr">
+        <is>
+          <t>Water steamed egg</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - FIRST COOK; no meat; set through</t>
+        </is>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n"/>
+      <c r="A275" s="8" t="n">
+        <v>46310</v>
+      </c>
       <c r="B275" s="3">
         <f>IF(A275="","",TEXT(A275,"ddd"))</f>
         <v/>
       </c>
+      <c r="C275" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried French beans with dried shrimp</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - FIRST COOK; as written</t>
+        </is>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n"/>
+      <c r="A276" s="8" t="n">
+        <v>46311</v>
+      </c>
       <c r="B276" s="3">
         <f>IF(A276="","",TEXT(A276,"ddd"))</f>
         <v/>
       </c>
+      <c r="C276" s="3" t="inlineStr">
+        <is>
+          <t>Taiwanese braised pork rice</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 12 Oct 2026) - as written; method in the video</t>
+        </is>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n"/>
+      <c r="A277" s="8" t="n">
+        <v>46313</v>
+      </c>
       <c r="B277" s="3">
         <f>IF(A277="","",TEXT(A277,"ddd"))</f>
         <v/>
       </c>
+      <c r="C277" s="3" t="inlineStr">
+        <is>
+          <t>Green curry</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 19 Oct 2026) - FIRST COOK; Sunday extra for 3; Dancing Chef packet; eggplant, long beans, carrot</t>
+        </is>
+      </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n"/>
+      <c r="A278" s="8" t="n">
+        <v>46313</v>
+      </c>
       <c r="B278" s="3">
         <f>IF(A278="","",TEXT(A278,"ddd"))</f>
         <v/>
       </c>
+      <c r="C278" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>planned Sunday extra (week of 19 Oct 2026) - jasmine rice, 3 cups (for 3 pax)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n"/>
+      <c r="A279" s="8" t="n">
+        <v>46314</v>
+      </c>
       <c r="B279" s="3">
         <f>IF(A279="","",TEXT(A279,"ddd"))</f>
         <v/>
       </c>
+      <c r="C279" s="3" t="inlineStr">
+        <is>
+          <t>Fragrant glutinous rice</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - FIRST COOK; for 5.5 pax; + 300g pork belly; wok then rice cooker, water 1:1; soak 2h</t>
+        </is>
+      </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n"/>
+      <c r="A280" s="8" t="n">
+        <v>46314</v>
+      </c>
       <c r="B280" s="3">
         <f>IF(A280="","",TEXT(A280,"ddd"))</f>
         <v/>
       </c>
+      <c r="C280" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - choy sum</t>
+        </is>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n"/>
+      <c r="A281" s="8" t="n">
+        <v>46315</v>
+      </c>
       <c r="B281" s="3">
         <f>IF(A281="","",TEXT(A281,"ddd"))</f>
         <v/>
       </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>Thai style steamed seabass</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - one fish; sauce finely chopped and simmered; chilli seeds out; no cabbage</t>
+        </is>
+      </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n"/>
+      <c r="A282" s="8" t="n">
+        <v>46315</v>
+      </c>
       <c r="B282" s="3">
         <f>IF(A282="","",TEXT(A282,"ddd"))</f>
         <v/>
       </c>
+      <c r="C282" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried French beans with dried shrimp</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - EARLY 5d after 15 Oct, cd 21; user approved; si ji dou; user asked for it again; now with a dried shrimp sambal (NoobCook technique)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n"/>
+      <c r="A283" s="8" t="n">
+        <v>46315</v>
+      </c>
       <c r="B283" s="3">
         <f>IF(A283="","",TEXT(A283,"ddd"))</f>
         <v/>
       </c>
+      <c r="C283" s="3" t="inlineStr">
+        <is>
+          <t>Steamed fish paste with minced meat</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - FIRST COOK; user's recipe, garlic-heavy, steam 15 min</t>
+        </is>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n"/>
+      <c r="A284" s="8" t="n">
+        <v>46315</v>
+      </c>
       <c r="B284" s="3">
         <f>IF(A284="","",TEXT(A284,"ddd"))</f>
         <v/>
       </c>
+      <c r="C284" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n"/>
+      <c r="A285" s="8" t="n">
+        <v>46316</v>
+      </c>
       <c r="B285" s="3">
         <f>IF(A285="","",TEXT(A285,"ddd"))</f>
         <v/>
       </c>
+      <c r="C285" s="3" t="inlineStr">
+        <is>
+          <t>Yam rice</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - FIRST COOK; with pork belly</t>
+        </is>
+      </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n"/>
+      <c r="A286" s="8" t="n">
+        <v>46316</v>
+      </c>
       <c r="B286" s="3">
         <f>IF(A286="","",TEXT(A286,"ddd"))</f>
         <v/>
       </c>
+      <c r="C286" s="3" t="inlineStr">
+        <is>
+          <t>Baked chicken wings</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - FIRST COOK; 12 individually frozen mid wings (2 per person)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n"/>
+      <c r="A287" s="8" t="n">
+        <v>46316</v>
+      </c>
       <c r="B287" s="3">
         <f>IF(A287="","",TEXT(A287,"ddd"))</f>
         <v/>
       </c>
+      <c r="C287" s="3" t="inlineStr">
+        <is>
+          <t>Fishball soup with cabbage</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - EARLY 14d after 7 Oct, cd 21; user approved; fishballs and wawa vegetable, no pork (user, 18 Oct)</t>
+        </is>
+      </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n"/>
+      <c r="A288" s="8" t="n">
+        <v>46317</v>
+      </c>
       <c r="B288" s="3">
         <f>IF(A288="","",TEXT(A288,"ddd"))</f>
         <v/>
       </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>Pan-fried threadfin with leek</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - household</t>
+        </is>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n"/>
+      <c r="A289" s="8" t="n">
+        <v>46317</v>
+      </c>
       <c r="B289" s="3">
         <f>IF(A289="","",TEXT(A289,"ddd"))</f>
         <v/>
       </c>
+      <c r="C289" s="3" t="inlineStr">
+        <is>
+          <t>Enoki with pork wrap</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - FIRST COOK; 16 rolls; enoki cooked soft</t>
+        </is>
+      </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n"/>
+      <c r="A290" s="8" t="n">
+        <v>46317</v>
+      </c>
       <c r="B290" s="3">
         <f>IF(A290="","",TEXT(A290,"ddd"))</f>
         <v/>
       </c>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n"/>
+      <c r="A291" s="8" t="n">
+        <v>46317</v>
+      </c>
       <c r="B291" s="3">
         <f>IF(A291="","",TEXT(A291,"ddd"))</f>
         <v/>
       </c>
+      <c r="C291" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - my addition</t>
+        </is>
+      </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n"/>
+      <c r="A292" s="8" t="n">
+        <v>46318</v>
+      </c>
       <c r="B292" s="3">
         <f>IF(A292="","",TEXT(A292,"ddd"))</f>
         <v/>
       </c>
+      <c r="C292" s="3" t="inlineStr">
+        <is>
+          <t>Pork krapow (Pad Kra Pao)</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - 500g pork; chilli seeds out; yolk firm; no prik nam pla</t>
+        </is>
+      </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n"/>
+      <c r="A293" s="8" t="n">
+        <v>46318</v>
+      </c>
       <c r="B293" s="3">
         <f>IF(A293="","",TEXT(A293,"ddd"))</f>
         <v/>
       </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>Stir-fried eggs and prawns</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026) - household</t>
+        </is>
+      </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n"/>
+      <c r="A294" s="8" t="n">
+        <v>46318</v>
+      </c>
       <c r="B294" s="3">
         <f>IF(A294="","",TEXT(A294,"ddd"))</f>
         <v/>
       </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried vegetable</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n"/>
+      <c r="A295" s="8" t="n">
+        <v>46318</v>
+      </c>
       <c r="B295" s="3">
         <f>IF(A295="","",TEXT(A295,"ddd"))</f>
         <v/>
+      </c>
+      <c r="C295" s="3" t="inlineStr">
+        <is>
+          <t>Steamed rice</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>planned (week of 19 Oct 2026)</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -5795,7 +6179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5976,7 +6360,11 @@
         <f>IF(C5="","Never cooked",IF(D5&lt;F5,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>recipes/pork-rib-king.md - ingredients only, method in the video (0WXGuOQq_xU). x1.5 for 5 pax</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -6264,7 +6652,11 @@
         <f>IF(C14="","Never cooked",IF(D14&lt;F14,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>recipes/roasted-vegetables.md - ingredients only; x1.25 for 5 pax; potato wedges left out when roast potatoes are served</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -6328,7 +6720,11 @@
         <f>IF(C16="","Never cooked",IF(D16&lt;F16,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>recipes/taiwanese-braised-pork-rice.md - ingredients only, method in the video (hqcVtqGoRG0)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -6360,7 +6756,11 @@
         <f>IF(C17="","Never cooked",IF(D17&lt;F17,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>recipes/steamed-fish-paste-with-minced-pork.md - user's own recipe, revised 17 Oct 2026: pork 1/3 and garlic paste 1/4-1/3 of the fish paste by volume; oil on top; steam 15 min. Never cooked</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -6584,7 +6984,11 @@
         <f>IF(C24="","Never cooked",IF(D24&lt;F24,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>recipes/soy-and-oyster-sauce-wings.md - oven method; individually frozen mid wings, x0.6 marinade. Never cooked</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -6744,7 +7148,11 @@
         <f>IF(C29="","Never cooked",IF(D29&lt;F29,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>recipes/thai-style-steamed-fish.md - ingredients only, method in the video (-2hNdMmJogU); one 700g fish, chillies cut to 4-5</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -6904,7 +7312,11 @@
         <f>IF(C34="","Never cooked",IF(D34&lt;F34,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>recipes/yam-rice.md - pork belly version (user, 17 Oct 2026), x1.6. Never cooked</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -7786,7 +8198,11 @@
         <f>IF(C62="","Never cooked",IF(D62&lt;F62,"Cooldown","Due"))</f>
         <v/>
       </c>
-      <c r="H62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>recipes/thai-green-curry.md - Dancing Chef packet; eggplant, long beans, carrot (the user's usual); Sunday for 3 pax</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -8855,6 +9271,11 @@
         <f>IF(C101="","Never cooked",IF(D101&lt;F101,"Cooldown","Due"))</f>
         <v/>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Household - no recipe file. Eggs cooked firm, prawns opaque</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9692,6 +10113,11 @@
         <f>IF(C128="","Never cooked",IF(D128&lt;F128,"Cooldown","Due"))</f>
         <v/>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>recipes/roast-potatoes.md - 1.5kg for 5 pax; skip the raw parsley</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10188,6 +10614,11 @@
         <f>IF(C144="","Never cooked",IF(D144&lt;F144,"Cooldown","Due"))</f>
         <v/>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>recipes/chicken-curry-potato.md - 4-6 pax as written; cut dried chillies to 3-4 for the child</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -11601,6 +12032,146 @@
       <c r="H192" s="3" t="inlineStr">
         <is>
           <t>recipes/japchae.md - PRE-SCALED to 5.5 pax (x1.6 from source 3-4). Side-dish portions: 80g beef. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>Beef hayashi rice</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>recipes/hayashi-rice.md - 2h simmer, as written (~5-6 pax). Never cooked. Added 9 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Greek lemon chicken</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>Chicken</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>recipes/greek-lemon-chicken.md - written for 8 bone-in thighs; made with 5 (marinade x0.6); own lemon rice and green beans not made. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Black pepper beef</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>Beef</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>recipes/black-pepper-beef.md - method inferred; 400g for 5 pax. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Water steamed egg</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Egg</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H196" s="3" t="inlineStr">
+        <is>
+          <t>Plain, no meat. Ah Gong steamed egg mix (recipes/steamed-egg.md) without the pork; 5 eggs for 5 pax; steam until set</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>Stir fried French beans with dried shrimp</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>Vegetable</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H197" s="3" t="inlineStr">
+        <is>
+          <t>recipes/zi-char-french-beans-with-dried-shrimp.md - as written (500g). Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>Fragrant glutinous rice</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>Rice</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>recipes/fragrant-glutinous-rice.md - household version (18 Oct 2026): + 300g pork belly, 2 sausages, wok then ordinary rice cooker, water 1:1, steam longer; soak 2h. Never cooked</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Enoki with pork wrap</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>Pork</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>recipes/enoki-mushroom-meat-roll.md - made with pork shabu slices, x2 (16 rolls). Enoki must be cooked soft and hot. Never cooked</t>
         </is>
       </c>
     </row>
